--- a/cold-call-campaign/exports/Cold-Call-Campaign.xlsx
+++ b/cold-call-campaign/exports/Cold-Call-Campaign.xlsx
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>A snapshot of your calling campaign, taken 18 August 2026 at 07:52 AM (Pakistan time).</t>
+          <t>A snapshot of your calling campaign, taken 18 August 2026 at 08:20 AM (Pakistan time).</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Attock</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18 Aug 2026 07:52 AM</t>
+          <t>18 Aug 2026 08:20 AM</t>
         </is>
       </c>
     </row>
